--- a/data/trans_orig/IP04F-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP04F-Habitat-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>121846</t>
+          <t>121656</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>132009</t>
+          <t>131937</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>135123</t>
+          <t>134957</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>146411</t>
+          <t>146350</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>261445</t>
+          <t>261513</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>276403</t>
+          <t>276454</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,22%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>5010</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15101</t>
+          <t>15291</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6975</t>
+          <t>7036</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18263</t>
+          <t>18429</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13929</t>
+          <t>13878</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28887</t>
+          <t>28819</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,93%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>176135</t>
+          <t>177563</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>190455</t>
+          <t>190102</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>196875</t>
+          <t>197282</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>210919</t>
+          <t>211259</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>88,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>378901</t>
+          <t>379738</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>397600</t>
+          <t>398516</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>93,09%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14600</t>
+          <t>14953</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>28920</t>
+          <t>27492</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12129</t>
+          <t>11789</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>26173</t>
+          <t>25766</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>30504</t>
+          <t>29588</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>49203</t>
+          <t>48366</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,3%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>133369</t>
+          <t>132847</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>145284</t>
+          <t>145077</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>139939</t>
+          <t>139493</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>152998</t>
+          <t>153371</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>277730</t>
+          <t>276985</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>295926</t>
+          <t>295379</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,05%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10092</t>
+          <t>10299</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22007</t>
+          <t>22529</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12518</t>
+          <t>12145</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25577</t>
+          <t>26023</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>24966</t>
+          <t>25513</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>43162</t>
+          <t>43907</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,68%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>169202</t>
+          <t>167990</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>186176</t>
+          <t>186048</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>180282</t>
+          <t>180525</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>195204</t>
+          <t>194915</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>354731</t>
+          <t>354452</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>376807</t>
+          <t>377040</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>91,01%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>20483</t>
+          <t>20611</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>37457</t>
+          <t>38669</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12415</t>
+          <t>12704</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>27337</t>
+          <t>27094</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>37471</t>
+          <t>37238</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>59547</t>
+          <t>59826</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,44%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>616173</t>
+          <t>616498</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>643538</t>
+          <t>642454</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>669599</t>
+          <t>668705</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>694777</t>
+          <t>694298</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1293194</t>
+          <t>1292995</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1330548</t>
+          <t>1330131</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,51%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>60499</t>
+          <t>61583</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>87864</t>
+          <t>87539</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>54791</t>
+          <t>55270</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>79969</t>
+          <t>80863</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>123057</t>
+          <t>123474</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>160411</t>
+          <t>160610</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,05%</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>115742</t>
+          <t>116141</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>126289</t>
+          <t>125964</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>132830</t>
+          <t>132086</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>142291</t>
+          <t>141773</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>252740</t>
+          <t>252846</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>265890</t>
+          <t>265857</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,23%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6224</t>
+          <t>6549</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16771</t>
+          <t>16372</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4359</t>
+          <t>4877</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13820</t>
+          <t>14564</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13272</t>
+          <t>13305</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26422</t>
+          <t>26316</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,43%</t>
         </is>
       </c>
     </row>
@@ -3021,12 +3021,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>184655</t>
+          <t>184726</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>195443</t>
+          <t>196045</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>195456</t>
+          <t>195112</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>208814</t>
+          <t>208995</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>383817</t>
+          <t>383604</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>401928</t>
+          <t>401216</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,19%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9512</t>
+          <t>8910</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20300</t>
+          <t>20229</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12207</t>
+          <t>12026</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>25565</t>
+          <t>25909</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>24047</t>
+          <t>24759</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>42158</t>
+          <t>42371</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,95%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>138897</t>
+          <t>138311</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>148647</t>
+          <t>148693</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>143534</t>
+          <t>142628</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>155752</t>
+          <t>155473</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>285955</t>
+          <t>285776</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>301898</t>
+          <t>301031</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,17%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6357</t>
+          <t>6311</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16107</t>
+          <t>16693</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8925</t>
+          <t>9204</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21143</t>
+          <t>22049</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>17784</t>
+          <t>18651</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>33727</t>
+          <t>33906</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,61%</t>
         </is>
       </c>
     </row>
@@ -3707,12 +3707,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>172069</t>
+          <t>170891</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>187941</t>
+          <t>187745</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>181861</t>
+          <t>182324</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>194649</t>
+          <t>195261</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>358579</t>
+          <t>357953</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>379469</t>
+          <t>378829</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3792,12 +3792,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,69%</t>
         </is>
       </c>
     </row>
@@ -3820,12 +3820,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19479</t>
+          <t>19675</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>35351</t>
+          <t>36529</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11087</t>
+          <t>10475</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23875</t>
+          <t>23412</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>33687</t>
+          <t>34327</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>54577</t>
+          <t>55203</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3905,12 +3905,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,36%</t>
         </is>
       </c>
     </row>
@@ -4050,12 +4050,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>624673</t>
+          <t>626864</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>649068</t>
+          <t>649469</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>668091</t>
+          <t>668554</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>692183</t>
+          <t>691154</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1300595</t>
+          <t>1297779</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1333907</t>
+          <t>1333413</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4135,12 +4135,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,73%</t>
         </is>
       </c>
     </row>
@@ -4163,12 +4163,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>50824</t>
+          <t>50423</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>75219</t>
+          <t>73028</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>45900</t>
+          <t>46929</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>69992</t>
+          <t>69529</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>104068</t>
+          <t>104562</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>137380</t>
+          <t>140196</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4248,12 +4248,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,75%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP04F-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP04F-Habitat-trans_orig.xlsx
@@ -542,7 +542,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -553,7 +553,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -721,72 +721,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>141740</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>135610</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>146379</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>92,41%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>88,41%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>95,43%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>128009</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>121656</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>131937</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>122576</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>132309</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>93,47%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>88,83%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>96,34%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>141740</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>134957</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>146350</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>92,41%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>261513</t>
+          <t>261882</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>276454</t>
+          <t>275742</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>94,97%</t>
         </is>
       </c>
     </row>
@@ -834,72 +834,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>11646</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>7007</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>17776</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>7,59%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>4,57%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>11,59%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>8938</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>5010</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>15291</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>4638</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>14371</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>6,53%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>3,66%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>11,17%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>11646</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>7036</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>18429</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>7,59%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13878</t>
+          <t>14590</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28819</t>
+          <t>28450</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,8%</t>
         </is>
       </c>
     </row>
@@ -947,57 +947,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>153386</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>153386</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>153386</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>136947</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>136947</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>136947</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>153386</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>153386</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>153386</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1064,72 +1064,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>297</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>205122</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>197700</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>211043</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>91,96%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>88,64%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>94,62%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>285</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>184647</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>177563</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>190102</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>177637</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>190451</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>90,05%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>86,59%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>92,71%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>297</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>205122</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>197282</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>211259</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>91,96%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>379738</t>
+          <t>378563</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>398516</t>
+          <t>397954</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>92,96%</t>
         </is>
       </c>
     </row>
@@ -1177,72 +1177,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>17926</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>12005</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>25348</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>8,04%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>5,38%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>11,36%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>20408</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>14953</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>27492</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>14604</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>27418</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>9,95%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>7,29%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>13,41%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>17926</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>11789</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>25766</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>8,04%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>29588</t>
+          <t>30150</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>48366</t>
+          <t>49541</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -1290,57 +1290,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>223048</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>223048</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>223048</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>317</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>205055</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>205055</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>205055</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>323</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>223048</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>223048</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>223048</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1407,72 +1407,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>147249</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>139942</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>153354</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>88,96%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>84,55%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>92,65%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>218</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>139980</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>132847</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>145077</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>133323</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>145038</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>90,09%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>85,5%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>93,37%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>147249</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>139493</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>153371</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>88,96%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>276985</t>
+          <t>277781</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>295379</t>
+          <t>295748</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>92,16%</t>
         </is>
       </c>
     </row>
@@ -1520,72 +1520,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>18267</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>12162</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>25574</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>11,04%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>7,35%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>15,45%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>15396</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>10299</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>22529</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>10338</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>22053</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>9,91%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>6,63%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>14,5%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>18267</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>12145</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>26023</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>11,04%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>25513</t>
+          <t>25144</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>43907</t>
+          <t>43111</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,43%</t>
         </is>
       </c>
     </row>
@@ -1633,57 +1633,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>165516</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>165516</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>165516</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>242</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>155376</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>155376</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>155376</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>165516</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>165516</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>165516</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1750,72 +1750,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>188223</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>180321</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>194873</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>90,66%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>86,85%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>93,86%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>178272</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>167990</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>186048</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>169102</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>186425</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>86,26%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>81,29%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>90,03%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>188223</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>180525</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>194915</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>90,66%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>81,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>354452</t>
+          <t>355046</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>377040</t>
+          <t>377616</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>91,15%</t>
         </is>
       </c>
     </row>
@@ -1863,72 +1863,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>19396</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>12746</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>27298</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>9,34%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>6,14%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>13,15%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>28387</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>20611</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>38669</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>20234</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>37557</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>13,74%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>9,97%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>18,71%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>19396</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>12704</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>27094</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>9,34%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>37238</t>
+          <t>36662</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>59826</t>
+          <t>59232</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,3%</t>
         </is>
       </c>
     </row>
@@ -1976,57 +1976,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>207619</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>207619</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>207619</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>271</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>206659</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>206659</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>206659</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>207619</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>207619</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>207619</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2093,72 +2093,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>973</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>682333</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>668068</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>694133</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>91,03%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>89,13%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>92,6%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>911</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>630907</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>616498</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>642454</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>617404</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>643024</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>89,61%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>87,57%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>91,25%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>973</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>682333</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>668705</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>694298</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>91,03%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1292995</t>
+          <t>1291404</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1330131</t>
+          <t>1331029</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,57%</t>
         </is>
       </c>
     </row>
@@ -2206,72 +2206,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>67235</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>55435</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>81500</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>8,97%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>7,4%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>10,87%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>105</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>73130</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>61583</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>87539</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>61013</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>86633</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>10,39%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>8,75%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>12,43%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>67235</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>55270</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>80863</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>8,97%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>123474</t>
+          <t>122576</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>160610</t>
+          <t>162201</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,16%</t>
         </is>
       </c>
     </row>
@@ -2319,57 +2319,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1068</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>749568</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>749568</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>749568</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1016</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>704037</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>704037</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>704037</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1068</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>749568</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>749568</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>749568</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2489,7 +2489,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2500,7 +2500,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2668,72 +2668,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>138106</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>132866</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>142230</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>94,17%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>90,6%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>96,99%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>169</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>121959</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>116141</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>125964</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>116185</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>126512</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>92,04%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>87,65%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>95,06%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>138106</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>132086</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>141773</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>94,17%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>252846</t>
+          <t>252410</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>265857</t>
+          <t>266288</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,39%</t>
         </is>
       </c>
     </row>
@@ -2781,72 +2781,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>8544</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4420</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>13784</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>5,83%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>3,01%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>9,4%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>10554</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>6549</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>16372</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>6001</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>16328</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>7,96%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>4,94%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>12,35%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>8544</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>4877</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>14564</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>5,83%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13305</t>
+          <t>12874</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26316</t>
+          <t>26752</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,58%</t>
         </is>
       </c>
     </row>
@@ -2894,57 +2894,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>146650</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>146650</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>146650</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>185</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>132513</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>132513</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>132513</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>146650</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>146650</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>146650</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3011,72 +3011,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>203048</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>195632</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>208804</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>91,87%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>88,51%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>94,47%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>307</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>190893</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>184726</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>196045</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>184837</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>196084</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>93,14%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>90,13%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>95,65%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>203048</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>195112</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>208995</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>91,87%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>383604</t>
+          <t>384758</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>401216</t>
+          <t>402000</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,37%</t>
         </is>
       </c>
     </row>
@@ -3124,72 +3124,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>17973</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>12217</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>25389</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>8,13%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>5,53%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>11,49%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>14062</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>8910</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>20229</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>8871</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>20118</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>6,86%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>4,35%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>9,87%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>17973</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>12026</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>25909</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>8,13%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>24759</t>
+          <t>23975</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>42371</t>
+          <t>41217</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,68%</t>
         </is>
       </c>
     </row>
@@ -3237,57 +3237,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>327</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>221021</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>221021</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>221021</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>330</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>204955</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>204955</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>204955</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>327</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>221021</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>221021</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>221021</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3354,72 +3354,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>150160</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>142770</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>155126</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>91,18%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>86,7%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>94,2%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>239</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>144341</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>138311</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>148693</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>139056</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>148445</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>93,12%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>89,23%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>95,93%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>150160</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>142628</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>155473</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>91,18%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>285776</t>
+          <t>286718</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>301031</t>
+          <t>302124</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,51%</t>
         </is>
       </c>
     </row>
@@ -3467,72 +3467,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>14517</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>9551</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>21907</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>8,82%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>5,8%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>13,3%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>10663</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>6311</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>16693</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>6559</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>15948</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>6,88%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>4,07%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>10,77%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>14517</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>9204</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>22049</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>8,82%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>18651</t>
+          <t>17558</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>33906</t>
+          <t>32964</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,31%</t>
         </is>
       </c>
     </row>
@@ -3580,57 +3580,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>164677</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>164677</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>164677</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>257</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>155004</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>155004</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>155004</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>245</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>164677</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>164677</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>164677</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3697,72 +3697,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>189152</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>181697</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>194792</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>91,94%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>88,32%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>94,68%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>244</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>180404</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>170891</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>187745</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>170755</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>188100</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>86,98%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>82,39%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>90,51%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>189152</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>182324</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>195261</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>91,94%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>82,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>357953</t>
+          <t>359213</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>378829</t>
+          <t>379460</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3792,12 +3792,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,84%</t>
         </is>
       </c>
     </row>
@@ -3810,72 +3810,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>16584</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>10944</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>24039</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>8,06%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>5,32%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>11,68%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>27016</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>19675</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>36529</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>19320</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>36665</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>13,02%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>9,49%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>17,61%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>16584</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>10475</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>23412</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>8,06%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>34327</t>
+          <t>33696</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>55203</t>
+          <t>53943</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3905,12 +3905,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,06%</t>
         </is>
       </c>
     </row>
@@ -3923,57 +3923,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>281</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4040,72 +4040,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>970</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>680466</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>667569</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>690857</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>92,19%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>90,45%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>93,6%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>959</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>637596</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>626864</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>649469</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>623377</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>647722</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>91,1%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>89,57%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>92,8%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>970</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>680466</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>668554</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>691154</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>92,19%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1297779</t>
+          <t>1298023</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1333413</t>
+          <t>1334574</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4135,12 +4135,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,81%</t>
         </is>
       </c>
     </row>
@@ -4153,72 +4153,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>57617</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>47226</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>70514</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>7,81%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>6,4%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>9,55%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>62296</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>50423</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>73028</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>52170</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>76515</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>8,9%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>7,2%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>10,43%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>57617</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>46929</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>69529</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>7,81%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>104562</t>
+          <t>103401</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>140196</t>
+          <t>139952</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4248,12 +4248,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,73%</t>
         </is>
       </c>
     </row>
@@ -4266,57 +4266,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1055</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>738083</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>738083</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>738083</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1053</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>699892</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>699892</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>699892</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1055</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>738083</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>738083</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>738083</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
